--- a/data/trans_camb/IP08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,76</t>
+          <t>-1,48; 11,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 3,69</t>
+          <t>-8,51; 3,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 14,32</t>
+          <t>-3,07; 13,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 10,8</t>
+          <t>-2,52; 11,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 4,09</t>
+          <t>-8,23; 3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 15,57</t>
+          <t>-2,37; 15,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 9,1</t>
+          <t>-0,5; 9,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,01</t>
+          <t>-7,24; 1,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 11,48</t>
+          <t>-0,61; 11,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 187,63</t>
+          <t>-14,52; 188,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 66,91</t>
+          <t>-63,73; 54,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 232,01</t>
+          <t>-29,58; 202,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 115,41</t>
+          <t>-15,02; 117,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 46,86</t>
+          <t>-53,16; 49,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 151,08</t>
+          <t>-19,06; 162,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 99,76</t>
+          <t>-4,71; 110,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 24,02</t>
+          <t>-51,06; 21,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 128,1</t>
+          <t>-6,09; 119,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,84</t>
+          <t>-1,88; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,64</t>
+          <t>-5,24; 3,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,07</t>
+          <t>-8,0; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 5,31</t>
+          <t>-4,26; 5,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -1,32</t>
+          <t>-9,86; -1,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,41</t>
+          <t>-6,87; 4,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,69</t>
+          <t>-1,9; 5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,2</t>
+          <t>-6,39; -0,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,91</t>
+          <t>-5,62; 1,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 91,58</t>
+          <t>-16,83; 96,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 48,67</t>
+          <t>-43,66; 48,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 5,23</t>
+          <t>-66,82; 11,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 45,64</t>
+          <t>-26,65; 45,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; -10,29</t>
+          <t>-62,48; -10,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 36,06</t>
+          <t>-41,81; 39,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 45,08</t>
+          <t>-14,21; 49,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -0,26</t>
+          <t>-46,12; 0,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 9,84</t>
+          <t>-44,24; 13,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 9,09</t>
+          <t>-3,59; 8,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,19</t>
+          <t>-11,78; -1,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 4,86</t>
+          <t>-6,49; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 4,62</t>
+          <t>-7,76; 3,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -3,32</t>
+          <t>-12,42; -3,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,82</t>
+          <t>-5,76; 5,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,38</t>
+          <t>-3,64; 4,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -3,53</t>
+          <t>-10,19; -3,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,81</t>
+          <t>-4,35; 3,76</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 126,11</t>
+          <t>-27,54; 111,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,68; -9,98</t>
+          <t>-79,02; -7,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 68,92</t>
+          <t>-46,62; 65,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 62,35</t>
+          <t>-54,83; 56,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,69; -38,38</t>
+          <t>-88,3; -34,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 88,73</t>
+          <t>-42,44; 76,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 53,9</t>
+          <t>-28,53; 53,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,75; -36,07</t>
+          <t>-78,37; -40,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 45,38</t>
+          <t>-33,29; 41,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,97</t>
+          <t>0,19; 8,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,02</t>
+          <t>-1,49; 6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 14,18</t>
+          <t>1,98; 14,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,53</t>
+          <t>-0,49; 9,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,54</t>
+          <t>-6,33; 2,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 16,34</t>
+          <t>-0,64; 15,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,88</t>
+          <t>1,12; 7,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,02</t>
+          <t>-2,5; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,38</t>
+          <t>2,2; 12,3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163,06%</t>
+          <t>163,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 312,16</t>
+          <t>-5,03; 348,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 245,51</t>
+          <t>-31,72; 248,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,52; 488,46</t>
+          <t>25,69; 552,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 161,95</t>
+          <t>-6,0; 158,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,46; 41,15</t>
+          <t>-58,82; 41,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 224,77</t>
+          <t>-10,59; 235,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,4; 163,42</t>
+          <t>8,9; 145,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 59,51</t>
+          <t>-34,99; 65,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,92; 212,28</t>
+          <t>24,92; 210,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,9</t>
+          <t>0,93; 6,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,7</t>
+          <t>-3,62; 0,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,45</t>
+          <t>-1,48; 4,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,83</t>
+          <t>-0,76; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,31</t>
+          <t>-7,1; -2,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,05</t>
+          <t>-1,39; 5,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,58</t>
+          <t>0,74; 4,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -1,51</t>
+          <t>-4,89; -1,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,08</t>
+          <t>-0,72; 4,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,67; 84,63</t>
+          <t>9,58; 87,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 10,26</t>
+          <t>-39,5; 9,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 63,12</t>
+          <t>-16,58; 67,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 46,35</t>
+          <t>-5,06; 48,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -21,96</t>
+          <t>-54,14; -21,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 59,46</t>
+          <t>-11,42; 59,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,16; 50,84</t>
+          <t>6,88; 50,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -16,51</t>
+          <t>-44,57; -15,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 43,31</t>
+          <t>-7,46; 45,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 11,71</t>
+          <t>-1,78; 11,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 3,27</t>
+          <t>-7,53; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 13,71</t>
+          <t>-2,39; 14,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,12</t>
+          <t>-2,33; 11,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 3,83</t>
+          <t>-9,04; 3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 15,68</t>
+          <t>-3,34; 14,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,76</t>
+          <t>-0,22; 9,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 1,89</t>
+          <t>-6,84; 2,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 11,7</t>
+          <t>-0,05; 11,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 188,01</t>
+          <t>-16,81; 174,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,73; 54,77</t>
+          <t>-60,86; 82,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 202,11</t>
+          <t>-22,92; 239,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 117,68</t>
+          <t>-15,02; 119,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 49,2</t>
+          <t>-55,36; 44,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 162,96</t>
+          <t>-24,55; 152,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 110,76</t>
+          <t>-1,63; 109,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 21,95</t>
+          <t>-49,6; 25,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 119,95</t>
+          <t>-5,49; 123,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,22</t>
+          <t>-2,08; 6,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,6</t>
+          <t>-4,91; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,69</t>
+          <t>-8,01; -0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,43</t>
+          <t>-4,32; 5,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -1,21</t>
+          <t>-10,21; -0,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,15</t>
+          <t>-6,65; 4,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 5,15</t>
+          <t>-2,22; 4,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,15</t>
+          <t>-6,26; -0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,35</t>
+          <t>-6,04; 1,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 96,07</t>
+          <t>-19,27; 87,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,66; 48,2</t>
+          <t>-44,98; 41,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 11,8</t>
+          <t>-67,46; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 45,77</t>
+          <t>-27,29; 51,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,48; -10,75</t>
+          <t>-62,0; -8,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 39,12</t>
+          <t>-42,14; 40,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 49,92</t>
+          <t>-16,37; 49,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 0,26</t>
+          <t>-46,53; 0,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 13,46</t>
+          <t>-44,88; 10,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,43</t>
+          <t>-4,55; 8,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -1,24</t>
+          <t>-11,08; -0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 4,53</t>
+          <t>-7,04; 5,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 3,96</t>
+          <t>-6,79; 4,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -3,15</t>
+          <t>-12,47; -3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 5,98</t>
+          <t>-5,66; 6,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,68</t>
+          <t>-3,79; 4,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -3,53</t>
+          <t>-10,33; -3,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,76</t>
+          <t>-4,85; 3,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 111,77</t>
+          <t>-31,8; 110,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,02; -7,57</t>
+          <t>-77,79; -8,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 65,73</t>
+          <t>-51,9; 69,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 56,96</t>
+          <t>-49,1; 62,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,3; -34,51</t>
+          <t>-88,55; -38,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 76,14</t>
+          <t>-42,39; 76,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 53,0</t>
+          <t>-30,45; 57,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,37; -40,36</t>
+          <t>-78,16; -36,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 41,8</t>
+          <t>-36,01; 39,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,31</t>
+          <t>0,12; 8,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,1</t>
+          <t>-1,61; 6,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 14,25</t>
+          <t>2,05; 13,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 9,85</t>
+          <t>-0,7; 9,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,64</t>
+          <t>-5,79; 2,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 15,26</t>
+          <t>-0,25; 16,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,63</t>
+          <t>1,08; 7,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,32</t>
+          <t>-3,03; 3,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,3</t>
+          <t>1,89; 11,81</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 348,67</t>
+          <t>-8,15; 321,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 248,39</t>
+          <t>-35,31; 265,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,69; 552,47</t>
+          <t>27,53; 502,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 158,01</t>
+          <t>-7,54; 144,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 41,99</t>
+          <t>-59,13; 44,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 235,43</t>
+          <t>-5,88; 241,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,9; 145,86</t>
+          <t>14,58; 158,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 65,41</t>
+          <t>-40,28; 61,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,92; 210,24</t>
+          <t>25,05; 227,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,05</t>
+          <t>0,9; 6,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,66</t>
+          <t>-3,91; 0,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,77</t>
+          <t>-1,19; 4,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,0</t>
+          <t>-0,64; 4,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -2,24</t>
+          <t>-7,08; -2,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,94</t>
+          <t>-1,62; 6,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,53</t>
+          <t>0,69; 4,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,46</t>
+          <t>-4,79; -1,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,53</t>
+          <t>-0,62; 4,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,58; 87,15</t>
+          <t>9,76; 87,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 9,05</t>
+          <t>-40,35; 14,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 67,62</t>
+          <t>-13,79; 67,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 48,68</t>
+          <t>-5,96; 47,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -21,59</t>
+          <t>-54,82; -20,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 59,36</t>
+          <t>-13,35; 61,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,88; 50,18</t>
+          <t>6,14; 48,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,57; -15,93</t>
+          <t>-44,41; -16,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 45,97</t>
+          <t>-6,39; 43,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 11,08</t>
+          <t>-2,84; 10,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 4,03</t>
+          <t>-9,58; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,03</t>
+          <t>-3,1; 15,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,05</t>
+          <t>-1,31; 11,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 3,83</t>
+          <t>-8,5; 3,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 14,57</t>
+          <t>-2,77; 15,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 9,03</t>
+          <t>-0,39; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 2,03</t>
+          <t>-6,73; 2,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 11,75</t>
+          <t>-0,87; 11,89</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-20,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>52,66%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-21,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,49%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 174,13</t>
+          <t>-19,13; 115,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 82,38</t>
+          <t>-56,9; 46,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 239,09</t>
+          <t>-22,44; 155,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 119,4</t>
+          <t>-13,06; 187,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 44,53</t>
+          <t>-62,8; 66,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 152,13</t>
+          <t>-26,64; 251,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 109,01</t>
+          <t>-4,23; 99,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 25,69</t>
+          <t>-50,26; 24,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 123,79</t>
+          <t>-7,51; 131,97</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,91</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,91</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-2,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,72</t>
+          <t>-4,18; 5,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,26</t>
+          <t>-10,09; -1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -0,1</t>
+          <t>-7,08; 3,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,99</t>
+          <t>-2,43; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -0,92</t>
+          <t>-4,86; 3,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 4,52</t>
+          <t>-7,78; 0,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,9</t>
+          <t>-1,85; 4,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,09</t>
+          <t>-6,42; -0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,03</t>
+          <t>-5,99; 0,73</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-40,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-13,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>22,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-9,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-40,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-40,33%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,37%</t>
+          <t>-37,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,77%</t>
+          <t>-22,26%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 87,88</t>
+          <t>-26,25; 45,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 41,95</t>
+          <t>-61,7; -10,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 2,93</t>
+          <t>-45,83; 32,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 51,73</t>
+          <t>-21,57; 91,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,0; -8,16</t>
+          <t>-41,69; 48,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 40,15</t>
+          <t>-65,57; 7,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 49,16</t>
+          <t>-14,16; 45,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 0,56</t>
+          <t>-48,06; -0,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 10,67</t>
+          <t>-45,05; 8,38</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,53</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-6,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,53</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,47</t>
+          <t>-6,88; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,93</t>
+          <t>-12,88; -3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 5,19</t>
+          <t>-5,79; 6,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,96</t>
+          <t>-3,98; 9,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -3,06</t>
+          <t>-11,85; -1,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,15</t>
+          <t>-7,06; 5,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 4,91</t>
+          <t>-4,19; 4,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -3,23</t>
+          <t>-10,25; -3,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,36</t>
+          <t>-4,55; 3,5</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-11,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-70,55%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-56,12%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,96%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-11,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-70,55%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>-9,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,71%</t>
+          <t>-3,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 110,39</t>
+          <t>-50,74; 62,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,79; -8,08</t>
+          <t>-89,69; -38,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 69,11</t>
+          <t>-42,86; 82,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 62,95</t>
+          <t>-29,26; 126,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,55; -38,66</t>
+          <t>-79,68; -9,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 76,03</t>
+          <t>-50,96; 72,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 57,61</t>
+          <t>-31,04; 53,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,16; -36,51</t>
+          <t>-77,75; -36,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 39,76</t>
+          <t>-36,28; 42,09</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,84</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,81</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,75</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,84</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,35</t>
+          <t>-0,15; 10,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,3</t>
+          <t>-6,27; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,61</t>
+          <t>-0,31; 13,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 9,66</t>
+          <t>0,21; 7,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,75</t>
+          <t>-1,33; 6,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 16,53</t>
+          <t>2,04; 10,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,72</t>
+          <t>1,17; 7,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,06</t>
+          <t>-2,89; 3,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 11,81</t>
+          <t>2,14; 10,36</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>55,28%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,28%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55,77%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>92,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>50,67%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>163,05%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>55,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-21,28%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>143,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 321,22</t>
+          <t>-4,73; 161,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 265,3</t>
+          <t>-59,46; 41,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,53; 502,8</t>
+          <t>-5,9; 201,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 144,9</t>
+          <t>-4,24; 312,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 44,45</t>
+          <t>-28,89; 245,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 241,54</t>
+          <t>31,57; 405,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,58; 158,78</t>
+          <t>15,4; 163,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 61,26</t>
+          <t>-37,28; 59,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,05; 227,27</t>
+          <t>23,06; 181,57</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,03</t>
+          <t>-0,72; 4,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,94</t>
+          <t>-7,22; -2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,81</t>
+          <t>-2,02; 5,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,95</t>
+          <t>0,79; 5,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -2,1</t>
+          <t>-3,9; 0,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,36</t>
+          <t>-1,33; 3,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,45</t>
+          <t>1,01; 4,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -1,5</t>
+          <t>-4,78; -1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,24</t>
+          <t>-1,17; 3,5</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-40,01%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-17,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-40,01%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,76; 87,89</t>
+          <t>-6,27; 46,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 14,23</t>
+          <t>-55,47; -21,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 67,04</t>
+          <t>-16,67; 52,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 47,31</t>
+          <t>7,67; 84,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -20,42</t>
+          <t>-40,67; 10,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 61,31</t>
+          <t>-15,43; 55,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14; 48,39</t>
+          <t>9,16; 50,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -16,04</t>
+          <t>-43,99; -16,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 43,93</t>
+          <t>-11,15; 37,9</t>
         </is>
       </c>
     </row>
